--- a/compare/output/dscale_energy_intensity_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_energy_intensity_downscaled_SSP245.xlsx
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1895.818662350746</v>
+        <v>3582.306005342686</v>
       </c>
       <c r="F54" t="n">
-        <v>1662.621086060707</v>
+        <v>3139.631036633496</v>
       </c>
       <c r="G54" t="n">
-        <v>1482.92100319883</v>
+        <v>2787.425146623555</v>
       </c>
       <c r="H54" t="n">
-        <v>1330.392388802022</v>
+        <v>2484.128655921776</v>
       </c>
       <c r="I54" t="n">
-        <v>1207.335630447164</v>
+        <v>2236.93134516011</v>
       </c>
       <c r="J54" t="n">
-        <v>1120.023214615919</v>
+        <v>2057.701653665098</v>
       </c>
       <c r="K54" t="n">
-        <v>1140.428174400802</v>
+        <v>1922.428038738472</v>
       </c>
       <c r="L54" t="n">
-        <v>1156.137980210365</v>
+        <v>1817.338857977998</v>
       </c>
       <c r="M54" t="n">
-        <v>1170.649739824276</v>
+        <v>1736.885740400094</v>
       </c>
       <c r="N54" t="n">
-        <v>1181.890102918429</v>
+        <v>1670.928115629457</v>
       </c>
       <c r="O54" t="n">
-        <v>1187.09905066025</v>
+        <v>1611.992448491052</v>
       </c>
       <c r="P54" t="n">
-        <v>1190.263691964681</v>
+        <v>1562.153916107444</v>
       </c>
       <c r="Q54" t="n">
-        <v>1193.874193940351</v>
+        <v>1521.801357803856</v>
       </c>
       <c r="R54" t="n">
-        <v>1193.30718288241</v>
+        <v>1482.950077014373</v>
       </c>
       <c r="S54" t="n">
-        <v>1189.260571640327</v>
+        <v>1445.262262557802</v>
       </c>
       <c r="T54" t="n">
-        <v>1182.746292299885</v>
+        <v>1409.288436441681</v>
       </c>
       <c r="U54" t="n">
-        <v>1174.033508767326</v>
+        <v>1374.942379718393</v>
       </c>
       <c r="V54" t="n">
-        <v>1164.447794262087</v>
+        <v>1342.795779797396</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>18598.92589647757</v>
+        <v>5005.284628918103</v>
       </c>
       <c r="F55" t="n">
-        <v>17196.42406289787</v>
+        <v>4417.56365416658</v>
       </c>
       <c r="G55" t="n">
-        <v>15864.26440820006</v>
+        <v>3949.978300526777</v>
       </c>
       <c r="H55" t="n">
-        <v>14503.87034328825</v>
+        <v>3542.289905786283</v>
       </c>
       <c r="I55" t="n">
-        <v>13269.47226046152</v>
+        <v>3206.211657705091</v>
       </c>
       <c r="J55" t="n">
-        <v>12306.52193541911</v>
+        <v>2960.841574320695</v>
       </c>
       <c r="K55" t="n">
-        <v>10669.45062427629</v>
+        <v>2773.483141035626</v>
       </c>
       <c r="L55" t="n">
-        <v>9358.384644795329</v>
+        <v>2625.653713716821</v>
       </c>
       <c r="M55" t="n">
-        <v>8308.113720281395</v>
+        <v>2510.586338621626</v>
       </c>
       <c r="N55" t="n">
-        <v>7437.053058950124</v>
+        <v>2414.420239206724</v>
       </c>
       <c r="O55" t="n">
-        <v>6691.766655552739</v>
+        <v>2327.293715197758</v>
       </c>
       <c r="P55" t="n">
-        <v>6059.275074205148</v>
+        <v>2252.207400354766</v>
       </c>
       <c r="Q55" t="n">
-        <v>5522.584849253876</v>
+        <v>2189.545931488969</v>
       </c>
       <c r="R55" t="n">
-        <v>5040.423470776667</v>
+        <v>2127.707190460234</v>
       </c>
       <c r="S55" t="n">
-        <v>4606.3075382267</v>
+        <v>2066.33118653763</v>
       </c>
       <c r="T55" t="n">
-        <v>4218.628438911887</v>
+        <v>2006.681735049379</v>
       </c>
       <c r="U55" t="n">
-        <v>3875.532741077958</v>
+        <v>1949.492299656248</v>
       </c>
       <c r="V55" t="n">
-        <v>3571.474803657406</v>
+        <v>1895.256433176701</v>
       </c>
     </row>
     <row r="56">
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>9062.680284830976</v>
+        <v>4633.968023971435</v>
       </c>
       <c r="F86" t="n">
-        <v>8352.846308860593</v>
+        <v>4174.020377239851</v>
       </c>
       <c r="G86" t="n">
-        <v>7891.904812767504</v>
+        <v>3895.952201260959</v>
       </c>
       <c r="H86" t="n">
-        <v>7498.422949440834</v>
+        <v>3704.176838727385</v>
       </c>
       <c r="I86" t="n">
-        <v>7173.88003848289</v>
+        <v>3576.959241270563</v>
       </c>
       <c r="J86" t="n">
-        <v>6888.344553816488</v>
+        <v>3478.096970550175</v>
       </c>
       <c r="K86" t="n">
-        <v>6517.379772930601</v>
+        <v>3332.464226867446</v>
       </c>
       <c r="L86" t="n">
-        <v>6163.143757813526</v>
+        <v>3187.018759027518</v>
       </c>
       <c r="M86" t="n">
-        <v>5878.007967643542</v>
+        <v>3071.06248349142</v>
       </c>
       <c r="N86" t="n">
-        <v>5598.362508725862</v>
+        <v>2953.95648015328</v>
       </c>
       <c r="O86" t="n">
-        <v>5292.334886314841</v>
+        <v>2819.255435557509</v>
       </c>
       <c r="P86" t="n">
-        <v>5012.841870407332</v>
+        <v>2695.664662798658</v>
       </c>
       <c r="Q86" t="n">
-        <v>4768.323075915328</v>
+        <v>2589.162936318442</v>
       </c>
       <c r="R86" t="n">
-        <v>4521.743125454189</v>
+        <v>2480.651618389604</v>
       </c>
       <c r="S86" t="n">
-        <v>4284.785916538853</v>
+        <v>2376.039723728454</v>
       </c>
       <c r="T86" t="n">
-        <v>4056.258498923678</v>
+        <v>2273.845364212183</v>
       </c>
       <c r="U86" t="n">
-        <v>3835.552644448964</v>
+        <v>2172.38467196296</v>
       </c>
       <c r="V86" t="n">
-        <v>3629.756632207423</v>
+        <v>2075.438569864819</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5048.962199461121</v>
+        <v>2581.656712041289</v>
       </c>
       <c r="F87" t="n">
-        <v>4659.407336790481</v>
+        <v>2328.363344708998</v>
       </c>
       <c r="G87" t="n">
-        <v>4402.165802082223</v>
+        <v>2173.192398264344</v>
       </c>
       <c r="H87" t="n">
-        <v>4181.026997439761</v>
+        <v>2065.402748079821</v>
       </c>
       <c r="I87" t="n">
-        <v>3998.373853373264</v>
+        <v>1993.624123644533</v>
       </c>
       <c r="J87" t="n">
-        <v>3837.911214092549</v>
+        <v>1937.857095089185</v>
       </c>
       <c r="K87" t="n">
-        <v>3630.478053964705</v>
+        <v>1856.334702400899</v>
       </c>
       <c r="L87" t="n">
-        <v>3432.809253607595</v>
+        <v>1775.137481340344</v>
       </c>
       <c r="M87" t="n">
-        <v>3273.707581711894</v>
+        <v>1710.40267238244</v>
       </c>
       <c r="N87" t="n">
-        <v>3117.374768657875</v>
+        <v>1644.871939709465</v>
       </c>
       <c r="O87" t="n">
-        <v>2945.787464153377</v>
+        <v>1569.236924477066</v>
       </c>
       <c r="P87" t="n">
-        <v>2788.366469487292</v>
+        <v>1499.449045677339</v>
       </c>
       <c r="Q87" t="n">
-        <v>2650.686130077079</v>
+        <v>1439.302281858986</v>
       </c>
       <c r="R87" t="n">
-        <v>2512.708620586331</v>
+        <v>1378.484919033532</v>
       </c>
       <c r="S87" t="n">
-        <v>2381.071657730686</v>
+        <v>1320.374215659368</v>
       </c>
       <c r="T87" t="n">
-        <v>2254.89712657871</v>
+        <v>1264.043546391442</v>
       </c>
       <c r="U87" t="n">
-        <v>2133.45342054474</v>
+        <v>1208.347776386379</v>
       </c>
       <c r="V87" t="n">
-        <v>2020.441498810676</v>
+        <v>1155.257125940766</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>8759.986573554996</v>
+        <v>4479.193394934263</v>
       </c>
       <c r="F88" t="n">
-        <v>8063.741087086787</v>
+        <v>4029.550930272797</v>
       </c>
       <c r="G88" t="n">
-        <v>7618.734081738871</v>
+        <v>3761.097544988757</v>
       </c>
       <c r="H88" t="n">
-        <v>7239.361609346191</v>
+        <v>3576.202060262588</v>
       </c>
       <c r="I88" t="n">
-        <v>6923.804449499396</v>
+        <v>3452.269368533495</v>
       </c>
       <c r="J88" t="n">
-        <v>6643.271189451268</v>
+        <v>3354.353316397917</v>
       </c>
       <c r="K88" t="n">
-        <v>6279.503722460916</v>
+        <v>3210.833532288153</v>
       </c>
       <c r="L88" t="n">
-        <v>5932.303951917012</v>
+        <v>3067.649355910507</v>
       </c>
       <c r="M88" t="n">
-        <v>5651.661312881546</v>
+        <v>2952.803929994257</v>
       </c>
       <c r="N88" t="n">
-        <v>5375.296512608028</v>
+        <v>2836.256484177326</v>
       </c>
       <c r="O88" t="n">
-        <v>5072.237763370718</v>
+        <v>2702.00850702218</v>
       </c>
       <c r="P88" t="n">
-        <v>4793.45985779418</v>
+        <v>2577.691593958714</v>
       </c>
       <c r="Q88" t="n">
-        <v>4548.740472349909</v>
+        <v>2469.931263137402</v>
       </c>
       <c r="R88" t="n">
-        <v>4303.963126344185</v>
+        <v>2361.176386767914</v>
       </c>
       <c r="S88" t="n">
-        <v>4070.70970795321</v>
+        <v>2257.328174211045</v>
       </c>
       <c r="T88" t="n">
-        <v>3846.917985760321</v>
+        <v>2156.493879948996</v>
       </c>
       <c r="U88" t="n">
-        <v>3631.281225691729</v>
+        <v>2056.689193327739</v>
       </c>
       <c r="V88" t="n">
-        <v>3430.16595244241</v>
+        <v>1961.315713444765</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>10335.19675713683</v>
+        <v>5284.636530113036</v>
       </c>
       <c r="F89" t="n">
-        <v>9507.942837321882</v>
+        <v>4751.236366769992</v>
       </c>
       <c r="G89" t="n">
-        <v>8967.728310516221</v>
+        <v>4427.047928309892</v>
       </c>
       <c r="H89" t="n">
-        <v>8506.041783391178</v>
+        <v>4201.934616865709</v>
       </c>
       <c r="I89" t="n">
-        <v>8124.292228901581</v>
+        <v>4050.843059984923</v>
       </c>
       <c r="J89" t="n">
-        <v>7789.182830389446</v>
+        <v>3932.952684622126</v>
       </c>
       <c r="K89" t="n">
-        <v>7360.020763064535</v>
+        <v>3763.323107833084</v>
       </c>
       <c r="L89" t="n">
-        <v>6951.779088323214</v>
+        <v>3594.829397756146</v>
       </c>
       <c r="M89" t="n">
-        <v>6621.742093920782</v>
+        <v>3459.638678941282</v>
       </c>
       <c r="N89" t="n">
-        <v>6296.650547511354</v>
+        <v>3322.405731864709</v>
       </c>
       <c r="O89" t="n">
-        <v>5940.416402597542</v>
+        <v>3164.491966635117</v>
       </c>
       <c r="P89" t="n">
-        <v>5612.429241176936</v>
+        <v>3018.093841582723</v>
       </c>
       <c r="Q89" t="n">
-        <v>5323.80173262567</v>
+        <v>2890.783595615479</v>
       </c>
       <c r="R89" t="n">
-        <v>5034.410435600372</v>
+        <v>2761.90355096793</v>
       </c>
       <c r="S89" t="n">
-        <v>4757.715497228656</v>
+        <v>2638.293075963926</v>
       </c>
       <c r="T89" t="n">
-        <v>4492.000818042485</v>
+        <v>2518.112501667099</v>
       </c>
       <c r="U89" t="n">
-        <v>4236.291196694228</v>
+        <v>2399.355429269292</v>
       </c>
       <c r="V89" t="n">
-        <v>3998.066036735979</v>
+        <v>2286.032177443205</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>75.46160738560546</v>
+        <v>4806.339378452491</v>
       </c>
       <c r="F90" t="n">
-        <v>127.1365924295624</v>
+        <v>4323.169057884835</v>
       </c>
       <c r="G90" t="n">
-        <v>165.1511567589832</v>
+        <v>4028.632783094683</v>
       </c>
       <c r="H90" t="n">
-        <v>195.7920441986119</v>
+        <v>3822.983689892194</v>
       </c>
       <c r="I90" t="n">
-        <v>222.9729676811502</v>
+        <v>3684.02937528344</v>
       </c>
       <c r="J90" t="n">
-        <v>247.8703661514045</v>
+        <v>3574.830296578039</v>
       </c>
       <c r="K90" t="n">
-        <v>265.9666099320844</v>
+        <v>3418.290454635811</v>
       </c>
       <c r="L90" t="n">
-        <v>280.6622541625769</v>
+        <v>3262.53300123141</v>
       </c>
       <c r="M90" t="n">
-        <v>294.3816986137011</v>
+        <v>3137.116810340985</v>
       </c>
       <c r="N90" t="n">
-        <v>304.6494820218512</v>
+        <v>3010.442228655597</v>
       </c>
       <c r="O90" t="n">
-        <v>309.866445467033</v>
+        <v>2865.810307023683</v>
       </c>
       <c r="P90" t="n">
-        <v>313.6907938162866</v>
+        <v>2732.284048723314</v>
       </c>
       <c r="Q90" t="n">
-        <v>317.5499071351427</v>
+        <v>2616.521099166355</v>
       </c>
       <c r="R90" t="n">
-        <v>319.5826549115212</v>
+        <v>2499.712284978582</v>
       </c>
       <c r="S90" t="n">
-        <v>320.6927135961432</v>
+        <v>2387.996208182829</v>
       </c>
       <c r="T90" t="n">
-        <v>320.7769291642305</v>
+        <v>2279.615427450692</v>
       </c>
       <c r="U90" t="n">
-        <v>319.8843156387557</v>
+        <v>2172.65923117288</v>
       </c>
       <c r="V90" t="n">
-        <v>318.7650484668197</v>
+        <v>2070.72626235788</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>9370.245087039122</v>
+        <v>4791.233359819779</v>
       </c>
       <c r="F91" t="n">
-        <v>8622.838967354064</v>
+        <v>4308.939040480743</v>
       </c>
       <c r="G91" t="n">
-        <v>8134.622091763016</v>
+        <v>4015.773073392209</v>
       </c>
       <c r="H91" t="n">
-        <v>7719.067178980274</v>
+        <v>3813.173790514056</v>
       </c>
       <c r="I91" t="n">
-        <v>7377.778374053612</v>
+        <v>3678.624732163045</v>
       </c>
       <c r="J91" t="n">
-        <v>7079.745809285333</v>
+        <v>3574.740238268934</v>
       </c>
       <c r="K91" t="n">
-        <v>6696.311534335855</v>
+        <v>3423.955549250785</v>
       </c>
       <c r="L91" t="n">
-        <v>6331.243597756297</v>
+        <v>3273.944744266336</v>
       </c>
       <c r="M91" t="n">
-        <v>6037.227408941448</v>
+        <v>3154.249314051827</v>
       </c>
       <c r="N91" t="n">
-        <v>5746.76848006795</v>
+        <v>3032.262374063123</v>
       </c>
       <c r="O91" t="n">
-        <v>5426.596225284681</v>
+        <v>2890.77717743419</v>
       </c>
       <c r="P91" t="n">
-        <v>5130.755657983324</v>
+        <v>2759.073012514343</v>
       </c>
       <c r="Q91" t="n">
-        <v>4870.097185877263</v>
+        <v>2644.425499115971</v>
       </c>
       <c r="R91" t="n">
-        <v>4608.378511131538</v>
+        <v>2528.180238153873</v>
       </c>
       <c r="S91" t="n">
-        <v>4357.950933299583</v>
+        <v>2416.611875892846</v>
       </c>
       <c r="T91" t="n">
-        <v>4117.0709393651</v>
+        <v>2307.935421789376</v>
       </c>
       <c r="U91" t="n">
-        <v>3884.669136334653</v>
+        <v>2200.203326533207</v>
       </c>
       <c r="V91" t="n">
-        <v>3667.77914010804</v>
+        <v>2097.179250411514</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>10110.29665218407</v>
+        <v>5169.639656969492</v>
       </c>
       <c r="F92" t="n">
-        <v>9303.208719040507</v>
+        <v>4648.928201382299</v>
       </c>
       <c r="G92" t="n">
-        <v>8771.696430287659</v>
+        <v>4330.273974041867</v>
       </c>
       <c r="H92" t="n">
-        <v>8317.773120516142</v>
+        <v>4108.931004618972</v>
       </c>
       <c r="I92" t="n">
-        <v>7943.919339116502</v>
+        <v>3960.907561815025</v>
       </c>
       <c r="J92" t="n">
-        <v>7616.653253454358</v>
+        <v>3845.838198072816</v>
       </c>
       <c r="K92" t="n">
-        <v>7197.565266913304</v>
+        <v>3680.256423324089</v>
       </c>
       <c r="L92" t="n">
-        <v>6799.173328745369</v>
+        <v>3515.915545082743</v>
       </c>
       <c r="M92" t="n">
-        <v>6477.430751658088</v>
+        <v>3384.240831304605</v>
       </c>
       <c r="N92" t="n">
-        <v>6160.752852917117</v>
+        <v>3250.699786620098</v>
       </c>
       <c r="O92" t="n">
-        <v>5813.601893824281</v>
+        <v>3096.937191507387</v>
       </c>
       <c r="P92" t="n">
-        <v>5493.84417768734</v>
+        <v>2954.324512033612</v>
       </c>
       <c r="Q92" t="n">
-        <v>5212.201418210709</v>
+        <v>2830.185479004849</v>
       </c>
       <c r="R92" t="n">
-        <v>4929.59619446781</v>
+        <v>2704.401917244344</v>
       </c>
       <c r="S92" t="n">
-        <v>4659.530752854924</v>
+        <v>2583.846749482696</v>
       </c>
       <c r="T92" t="n">
-        <v>4400.47850455502</v>
+        <v>2466.807194492097</v>
       </c>
       <c r="U92" t="n">
-        <v>4151.326961877215</v>
+        <v>2351.233289244849</v>
       </c>
       <c r="V92" t="n">
-        <v>3919.051337911093</v>
+        <v>2240.852797621503</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4142.149855415867</v>
+        <v>2117.981587933788</v>
       </c>
       <c r="F93" t="n">
-        <v>3829.076347942465</v>
+        <v>1913.436703084651</v>
       </c>
       <c r="G93" t="n">
-        <v>3621.762321422235</v>
+        <v>1787.935007274405</v>
       </c>
       <c r="H93" t="n">
-        <v>3440.485486648245</v>
+        <v>1699.579596893051</v>
       </c>
       <c r="I93" t="n">
-        <v>3288.72340928825</v>
+        <v>1639.786214407223</v>
       </c>
       <c r="J93" t="n">
-        <v>3154.6577809686</v>
+        <v>1592.865395357621</v>
       </c>
       <c r="K93" t="n">
-        <v>2982.38953634945</v>
+        <v>1524.954320094702</v>
       </c>
       <c r="L93" t="n">
-        <v>2819.00134393681</v>
+        <v>1457.731722311323</v>
       </c>
       <c r="M93" t="n">
-        <v>2688.343109654694</v>
+        <v>1404.569322187974</v>
       </c>
       <c r="N93" t="n">
-        <v>2560.777171785637</v>
+        <v>1351.185156212248</v>
       </c>
       <c r="O93" t="n">
-        <v>2421.084363686693</v>
+        <v>1289.724743221093</v>
       </c>
       <c r="P93" t="n">
-        <v>2292.892387544078</v>
+        <v>1233.006973767993</v>
       </c>
       <c r="Q93" t="n">
-        <v>2180.52123094017</v>
+        <v>1184.006339990838</v>
       </c>
       <c r="R93" t="n">
-        <v>2067.638327208533</v>
+        <v>1134.31705878549</v>
       </c>
       <c r="S93" t="n">
-        <v>1959.981356217771</v>
+        <v>1086.867267313517</v>
       </c>
       <c r="T93" t="n">
-        <v>1856.889357191099</v>
+        <v>1040.92953095746</v>
       </c>
       <c r="U93" t="n">
-        <v>1757.812604432575</v>
+        <v>995.5919034389331</v>
       </c>
       <c r="V93" t="n">
-        <v>1665.608571076763</v>
+        <v>952.3691588586471</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>70.02595520531688</v>
+        <v>3950.891853760582</v>
       </c>
       <c r="F94" t="n">
-        <v>110.9821947412839</v>
+        <v>3553.300273099702</v>
       </c>
       <c r="G94" t="n">
-        <v>143.0496800441258</v>
+        <v>3311.819579548981</v>
       </c>
       <c r="H94" t="n">
-        <v>171.8571535397664</v>
+        <v>3144.752662495953</v>
       </c>
       <c r="I94" t="n">
-        <v>199.5027878142581</v>
+        <v>3033.355631014192</v>
       </c>
       <c r="J94" t="n">
-        <v>225.4119119404274</v>
+        <v>2946.54851896536</v>
       </c>
       <c r="K94" t="n">
-        <v>244.9254753637331</v>
+        <v>2820.523727952633</v>
       </c>
       <c r="L94" t="n">
-        <v>261.3908943967714</v>
+        <v>2695.049825488386</v>
       </c>
       <c r="M94" t="n">
-        <v>277.4588426088357</v>
+        <v>2594.737740887001</v>
       </c>
       <c r="N94" t="n">
-        <v>290.3677417059432</v>
+        <v>2493.265264977575</v>
       </c>
       <c r="O94" t="n">
-        <v>298.0947802747519</v>
+        <v>2376.536932565509</v>
       </c>
       <c r="P94" t="n">
-        <v>303.8878749738734</v>
+        <v>2268.53733545819</v>
       </c>
       <c r="Q94" t="n">
-        <v>309.5131002828255</v>
+        <v>2175.053871428165</v>
       </c>
       <c r="R94" t="n">
-        <v>313.6812098238429</v>
+        <v>2080.779775941365</v>
       </c>
       <c r="S94" t="n">
-        <v>317.5136195505725</v>
+        <v>1990.966417791529</v>
       </c>
       <c r="T94" t="n">
-        <v>320.7076693022269</v>
+        <v>1904.047892809452</v>
       </c>
       <c r="U94" t="n">
-        <v>322.7068566040774</v>
+        <v>1818.099824614774</v>
       </c>
       <c r="V94" t="n">
-        <v>323.8977000895234</v>
+        <v>1735.927411710513</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7678.285403021724</v>
+        <v>3926.093376155954</v>
       </c>
       <c r="F95" t="n">
-        <v>7083.585612791748</v>
+        <v>3539.755144345479</v>
       </c>
       <c r="G95" t="n">
-        <v>6691.103753892739</v>
+        <v>3303.159505507513</v>
       </c>
       <c r="H95" t="n">
-        <v>6353.935678253963</v>
+        <v>3138.806857501648</v>
       </c>
       <c r="I95" t="n">
-        <v>6075.019353858535</v>
+        <v>3029.05770686291</v>
       </c>
       <c r="J95" t="n">
-        <v>5829.997910904535</v>
+        <v>2943.711353842102</v>
       </c>
       <c r="K95" t="n">
-        <v>5513.454573382372</v>
+        <v>2819.13756331356</v>
       </c>
       <c r="L95" t="n">
-        <v>5211.694490518291</v>
+        <v>2695.015524597004</v>
       </c>
       <c r="M95" t="n">
-        <v>4968.112114266649</v>
+        <v>2595.672345442991</v>
       </c>
       <c r="N95" t="n">
-        <v>4728.171883982995</v>
+        <v>2494.803427644086</v>
       </c>
       <c r="O95" t="n">
-        <v>4464.876256342738</v>
+        <v>2378.463745245553</v>
       </c>
       <c r="P95" t="n">
-        <v>4222.632401720241</v>
+        <v>2270.728110635259</v>
       </c>
       <c r="Q95" t="n">
-        <v>4009.8379601755</v>
+        <v>2177.31132346421</v>
       </c>
       <c r="R95" t="n">
-        <v>3796.29674659926</v>
+        <v>2082.667990429843</v>
       </c>
       <c r="S95" t="n">
-        <v>3592.220706700457</v>
+        <v>1991.991959871874</v>
       </c>
       <c r="T95" t="n">
-        <v>3396.236140553961</v>
+        <v>1903.851987247322</v>
       </c>
       <c r="U95" t="n">
-        <v>3207.492753826497</v>
+        <v>1816.66339632441</v>
       </c>
       <c r="V95" t="n">
-        <v>3031.429466834131</v>
+        <v>1733.324372619447</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7574.575663108725</v>
+        <v>3873.064073184603</v>
       </c>
       <c r="F96" t="n">
-        <v>6978.119547756208</v>
+        <v>3487.052450168309</v>
       </c>
       <c r="G96" t="n">
-        <v>6598.884679223936</v>
+        <v>3257.634234302771</v>
       </c>
       <c r="H96" t="n">
-        <v>6276.794457697392</v>
+        <v>3100.699548212282</v>
       </c>
       <c r="I96" t="n">
-        <v>6009.901340169135</v>
+        <v>2996.589296524088</v>
       </c>
       <c r="J96" t="n">
-        <v>5772.621968656026</v>
+        <v>2914.740809558747</v>
       </c>
       <c r="K96" t="n">
-        <v>5461.882591544028</v>
+        <v>2792.767796542722</v>
       </c>
       <c r="L96" t="n">
-        <v>5164.425617865396</v>
+        <v>2670.572352446435</v>
       </c>
       <c r="M96" t="n">
-        <v>4924.313997685234</v>
+        <v>2572.789295025377</v>
       </c>
       <c r="N96" t="n">
-        <v>4687.489781213092</v>
+        <v>2473.337657801662</v>
       </c>
       <c r="O96" t="n">
-        <v>4426.862451107663</v>
+        <v>2358.21358546952</v>
       </c>
       <c r="P96" t="n">
-        <v>4186.684442864915</v>
+        <v>2251.397031601493</v>
       </c>
       <c r="Q96" t="n">
-        <v>3975.577422371955</v>
+        <v>2158.708113647303</v>
       </c>
       <c r="R96" t="n">
-        <v>3764.028338654127</v>
+        <v>2064.965375271577</v>
       </c>
       <c r="S96" t="n">
-        <v>3562.329944785551</v>
+        <v>1975.416653880686</v>
       </c>
       <c r="T96" t="n">
-        <v>3368.981335225164</v>
+        <v>1888.573569274649</v>
       </c>
       <c r="U96" t="n">
-        <v>3182.71368813783</v>
+        <v>1802.629000899857</v>
       </c>
       <c r="V96" t="n">
-        <v>3008.881030304895</v>
+        <v>1720.431526181852</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8261.19365249363</v>
+        <v>4224.148488342107</v>
       </c>
       <c r="F97" t="n">
-        <v>7608.102460976289</v>
+        <v>3801.862686088124</v>
       </c>
       <c r="G97" t="n">
-        <v>7192.655156477697</v>
+        <v>3550.75756164617</v>
       </c>
       <c r="H97" t="n">
-        <v>6838.727973748087</v>
+        <v>3378.291400414214</v>
       </c>
       <c r="I97" t="n">
-        <v>6544.191666840631</v>
+        <v>3262.991119706563</v>
       </c>
       <c r="J97" t="n">
-        <v>6282.209063580889</v>
+        <v>3172.044043636318</v>
       </c>
       <c r="K97" t="n">
-        <v>5941.01995616365</v>
+        <v>3037.760137481101</v>
       </c>
       <c r="L97" t="n">
-        <v>5615.090113085566</v>
+        <v>2903.615139827938</v>
       </c>
       <c r="M97" t="n">
-        <v>5351.98491736406</v>
+        <v>2796.233040580906</v>
       </c>
       <c r="N97" t="n">
-        <v>5092.917845296886</v>
+        <v>2687.260363811225</v>
       </c>
       <c r="O97" t="n">
-        <v>4808.4577685747</v>
+        <v>2561.491476245394</v>
       </c>
       <c r="P97" t="n">
-        <v>4546.625363277335</v>
+        <v>2444.955903976365</v>
       </c>
       <c r="Q97" t="n">
-        <v>4316.427872068782</v>
+        <v>2343.787299167919</v>
       </c>
       <c r="R97" t="n">
-        <v>4085.384315843923</v>
+        <v>2241.26292309347</v>
       </c>
       <c r="S97" t="n">
-        <v>3864.532788722645</v>
+        <v>2142.997012805495</v>
       </c>
       <c r="T97" t="n">
-        <v>3652.519873056621</v>
+        <v>2047.518762236754</v>
       </c>
       <c r="U97" t="n">
-        <v>3448.480108490328</v>
+        <v>1953.154088521335</v>
       </c>
       <c r="V97" t="n">
-        <v>3258.435532916393</v>
+        <v>1863.122921907904</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1507.41321824189</v>
+        <v>3859.045396010622</v>
       </c>
       <c r="F98" t="n">
-        <v>1454.985894900144</v>
+        <v>3463.904980166563</v>
       </c>
       <c r="G98" t="n">
-        <v>1403.624152843873</v>
+        <v>3037.099480275522</v>
       </c>
       <c r="H98" t="n">
-        <v>1333.242681237435</v>
+        <v>2663.374330728261</v>
       </c>
       <c r="I98" t="n">
-        <v>1266.624731763594</v>
+        <v>2387.371914051002</v>
       </c>
       <c r="J98" t="n">
-        <v>1207.459629407226</v>
+        <v>2191.075219923017</v>
       </c>
       <c r="K98" t="n">
-        <v>1247.015256345618</v>
+        <v>2030.370710091717</v>
       </c>
       <c r="L98" t="n">
-        <v>1266.145504393236</v>
+        <v>1896.729628148744</v>
       </c>
       <c r="M98" t="n">
-        <v>1278.078447665855</v>
+        <v>1791.557824355707</v>
       </c>
       <c r="N98" t="n">
-        <v>1279.360303264091</v>
+        <v>1698.260195346643</v>
       </c>
       <c r="O98" t="n">
-        <v>1270.371583704378</v>
+        <v>1611.185904718598</v>
       </c>
       <c r="P98" t="n">
-        <v>1258.517620809341</v>
+        <v>1535.377376187483</v>
       </c>
       <c r="Q98" t="n">
-        <v>1248.23651684641</v>
+        <v>1472.773683195422</v>
       </c>
       <c r="R98" t="n">
-        <v>1230.226838435392</v>
+        <v>1410.409170171307</v>
       </c>
       <c r="S98" t="n">
-        <v>1207.757687551267</v>
+        <v>1350.597826471271</v>
       </c>
       <c r="T98" t="n">
-        <v>1183.991060179466</v>
+        <v>1294.763608937509</v>
       </c>
       <c r="U98" t="n">
-        <v>1158.779130794461</v>
+        <v>1242.54827803848</v>
       </c>
       <c r="V98" t="n">
-        <v>1131.835445611277</v>
+        <v>1193.259097967966</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1504.514386473562</v>
+        <v>4531.749487417253</v>
       </c>
       <c r="F99" t="n">
-        <v>1274.074586314609</v>
+        <v>4043.212833930813</v>
       </c>
       <c r="G99" t="n">
-        <v>1063.480707052951</v>
+        <v>3512.337468647284</v>
       </c>
       <c r="H99" t="n">
-        <v>905.0928263161899</v>
+        <v>3049.283226851282</v>
       </c>
       <c r="I99" t="n">
-        <v>799.1731331054151</v>
+        <v>2707.245089821614</v>
       </c>
       <c r="J99" t="n">
-        <v>729.8492354500376</v>
+        <v>2463.638403688778</v>
       </c>
       <c r="K99" t="n">
-        <v>736.7888574138727</v>
+        <v>2266.001185503859</v>
       </c>
       <c r="L99" t="n">
-        <v>740.7604181385685</v>
+        <v>2103.031623043726</v>
       </c>
       <c r="M99" t="n">
-        <v>745.693368395696</v>
+        <v>1974.761233656903</v>
       </c>
       <c r="N99" t="n">
-        <v>747.0864848511691</v>
+        <v>1861.803673667418</v>
       </c>
       <c r="O99" t="n">
-        <v>743.7702215136577</v>
+        <v>1757.410848629748</v>
       </c>
       <c r="P99" t="n">
-        <v>739.1468950105881</v>
+        <v>1666.481311064178</v>
       </c>
       <c r="Q99" t="n">
-        <v>735.466226097116</v>
+        <v>1590.737788950271</v>
       </c>
       <c r="R99" t="n">
-        <v>727.3744522671163</v>
+        <v>1516.093471027476</v>
       </c>
       <c r="S99" t="n">
-        <v>716.4941001606829</v>
+        <v>1444.917426133699</v>
       </c>
       <c r="T99" t="n">
-        <v>704.2758071408605</v>
+        <v>1378.480017599176</v>
       </c>
       <c r="U99" t="n">
-        <v>691.0305556720107</v>
+        <v>1316.437062884113</v>
       </c>
       <c r="V99" t="n">
-        <v>676.6055008869803</v>
+        <v>1258.049286091147</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1701.572897114538</v>
+        <v>3316.384400225985</v>
       </c>
       <c r="F100" t="n">
-        <v>1663.991715440209</v>
+        <v>2994.200427796569</v>
       </c>
       <c r="G100" t="n">
-        <v>1593.320089559491</v>
+        <v>2638.185867049338</v>
       </c>
       <c r="H100" t="n">
-        <v>1499.403055971768</v>
+        <v>2323.192950760167</v>
       </c>
       <c r="I100" t="n">
-        <v>1413.356314551987</v>
+        <v>2089.958978360337</v>
       </c>
       <c r="J100" t="n">
-        <v>1340.309092930787</v>
+        <v>1924.411051078443</v>
       </c>
       <c r="K100" t="n">
-        <v>1378.945883188372</v>
+        <v>1788.630140019555</v>
       </c>
       <c r="L100" t="n">
-        <v>1397.613449971361</v>
+        <v>1675.840677234619</v>
       </c>
       <c r="M100" t="n">
-        <v>1410.275792982577</v>
+        <v>1587.578063297426</v>
       </c>
       <c r="N100" t="n">
-        <v>1411.973517766381</v>
+        <v>1509.241588819751</v>
       </c>
       <c r="O100" t="n">
-        <v>1402.221546880645</v>
+        <v>1435.788558491307</v>
       </c>
       <c r="P100" t="n">
-        <v>1387.563478190755</v>
+        <v>1371.587065503957</v>
       </c>
       <c r="Q100" t="n">
-        <v>1372.936839283621</v>
+        <v>1318.486612968225</v>
       </c>
       <c r="R100" t="n">
-        <v>1349.584334034409</v>
+        <v>1265.192780297096</v>
       </c>
       <c r="S100" t="n">
-        <v>1321.703427238961</v>
+        <v>1213.924709451682</v>
       </c>
       <c r="T100" t="n">
-        <v>1292.395199221909</v>
+        <v>1165.956265811938</v>
       </c>
       <c r="U100" t="n">
-        <v>1262.581798060565</v>
+        <v>1121.214762666226</v>
       </c>
       <c r="V100" t="n">
-        <v>1232.611913355816</v>
+        <v>1079.243542411877</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1680.078420384959</v>
+        <v>6035.44649573795</v>
       </c>
       <c r="F101" t="n">
-        <v>1537.690549564783</v>
+        <v>5384.605947893599</v>
       </c>
       <c r="G101" t="n">
-        <v>1388.670946658876</v>
+        <v>4685.613400322341</v>
       </c>
       <c r="H101" t="n">
-        <v>1254.26579916403</v>
+        <v>4076.774619114579</v>
       </c>
       <c r="I101" t="n">
-        <v>1153.180945357577</v>
+        <v>3627.08747812535</v>
       </c>
       <c r="J101" t="n">
-        <v>1079.45512588467</v>
+        <v>3306.596129638252</v>
       </c>
       <c r="K101" t="n">
-        <v>1105.447765784249</v>
+        <v>3045.853850885256</v>
       </c>
       <c r="L101" t="n">
-        <v>1120.663657056038</v>
+        <v>2830.410385550248</v>
       </c>
       <c r="M101" t="n">
-        <v>1133.746196500043</v>
+        <v>2660.817982903321</v>
       </c>
       <c r="N101" t="n">
-        <v>1138.389501743024</v>
+        <v>2511.087168415561</v>
       </c>
       <c r="O101" t="n">
-        <v>1133.343879801669</v>
+        <v>2372.206427474024</v>
       </c>
       <c r="P101" t="n">
-        <v>1124.114118789023</v>
+        <v>2250.877910859372</v>
       </c>
       <c r="Q101" t="n">
-        <v>1115.294217135484</v>
+        <v>2149.678377306621</v>
       </c>
       <c r="R101" t="n">
-        <v>1099.776603399381</v>
+        <v>2049.782147832804</v>
       </c>
       <c r="S101" t="n">
-        <v>1081.210613825829</v>
+        <v>1954.637432592212</v>
       </c>
       <c r="T101" t="n">
-        <v>1061.586838816412</v>
+        <v>1865.955689133096</v>
       </c>
       <c r="U101" t="n">
-        <v>1040.613852163938</v>
+        <v>1783.141295440986</v>
       </c>
       <c r="V101" t="n">
-        <v>1018.17866572311</v>
+        <v>1705.223738004648</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1721.563118927531</v>
+        <v>3373.626040946614</v>
       </c>
       <c r="F102" t="n">
-        <v>1501.705187369455</v>
+        <v>3030.94033745448</v>
       </c>
       <c r="G102" t="n">
-        <v>1277.994478747745</v>
+        <v>2647.064984780016</v>
       </c>
       <c r="H102" t="n">
-        <v>1094.893885862327</v>
+        <v>2307.509416053893</v>
       </c>
       <c r="I102" t="n">
-        <v>964.6381679642611</v>
+        <v>2055.429735793073</v>
       </c>
       <c r="J102" t="n">
-        <v>874.6642410059853</v>
+        <v>1875.797490807627</v>
       </c>
       <c r="K102" t="n">
-        <v>874.8345968239433</v>
+        <v>1729.806991955208</v>
       </c>
       <c r="L102" t="n">
-        <v>871.1967189363771</v>
+        <v>1609.395183108644</v>
       </c>
       <c r="M102" t="n">
-        <v>869.9164192897269</v>
+        <v>1515.012198108058</v>
       </c>
       <c r="N102" t="n">
-        <v>866.1569667114417</v>
+        <v>1432.020353528339</v>
       </c>
       <c r="O102" t="n">
-        <v>858.5142589197951</v>
+        <v>1355.293507207362</v>
       </c>
       <c r="P102" t="n">
-        <v>850.0684441120136</v>
+        <v>1288.600810430307</v>
       </c>
       <c r="Q102" t="n">
-        <v>842.9762252408564</v>
+        <v>1233.315443155284</v>
       </c>
       <c r="R102" t="n">
-        <v>831.066221697651</v>
+        <v>1178.569525176904</v>
       </c>
       <c r="S102" t="n">
-        <v>816.2315543945418</v>
+        <v>1126.218764607581</v>
       </c>
       <c r="T102" t="n">
-        <v>799.7265803379925</v>
+        <v>1077.211605736253</v>
       </c>
       <c r="U102" t="n">
-        <v>782.8247529678781</v>
+        <v>1031.521127633706</v>
       </c>
       <c r="V102" t="n">
-        <v>765.8686094151568</v>
+        <v>988.700175056133</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1760.575093608728</v>
+        <v>3877.651995597629</v>
       </c>
       <c r="F103" t="n">
-        <v>1732.098466818463</v>
+        <v>3492.712888789154</v>
       </c>
       <c r="G103" t="n">
-        <v>1687.158844403203</v>
+        <v>3073.36922703478</v>
       </c>
       <c r="H103" t="n">
-        <v>1606.980997513408</v>
+        <v>2703.93767307702</v>
       </c>
       <c r="I103" t="n">
-        <v>1522.353490343204</v>
+        <v>2429.999387268731</v>
       </c>
       <c r="J103" t="n">
-        <v>1442.921853691108</v>
+        <v>2234.522538004208</v>
       </c>
       <c r="K103" t="n">
-        <v>1477.571621418432</v>
+        <v>2073.21682761311</v>
       </c>
       <c r="L103" t="n">
-        <v>1486.271203120848</v>
+        <v>1938.243896975129</v>
       </c>
       <c r="M103" t="n">
-        <v>1486.662881250242</v>
+        <v>1831.633490838578</v>
       </c>
       <c r="N103" t="n">
-        <v>1476.429140448456</v>
+        <v>1736.90072872372</v>
       </c>
       <c r="O103" t="n">
-        <v>1455.553528761805</v>
+        <v>1648.276582410572</v>
       </c>
       <c r="P103" t="n">
-        <v>1431.502219886628</v>
+        <v>1570.840394470661</v>
       </c>
       <c r="Q103" t="n">
-        <v>1408.511418407699</v>
+        <v>1506.48101407179</v>
       </c>
       <c r="R103" t="n">
-        <v>1376.286525594875</v>
+        <v>1441.97799802511</v>
       </c>
       <c r="S103" t="n">
-        <v>1339.920580339588</v>
+        <v>1379.985360739573</v>
       </c>
       <c r="T103" t="n">
-        <v>1303.533743174727</v>
+        <v>1322.12229134533</v>
       </c>
       <c r="U103" t="n">
-        <v>1267.923998649007</v>
+        <v>1268.255779965946</v>
       </c>
       <c r="V103" t="n">
-        <v>1230.114931741077</v>
+        <v>1217.119398093532</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>11829.30722815681</v>
+        <v>2267.755526579958</v>
       </c>
       <c r="F104" t="n">
-        <v>10430.02754420247</v>
+        <v>2060.943753532114</v>
       </c>
       <c r="G104" t="n">
-        <v>8980.541128816971</v>
+        <v>1815.920934752525</v>
       </c>
       <c r="H104" t="n">
-        <v>7665.2535238646</v>
+        <v>1592.445761794301</v>
       </c>
       <c r="I104" t="n">
-        <v>6682.316314338573</v>
+        <v>1424.532029992259</v>
       </c>
       <c r="J104" t="n">
-        <v>5978.96717538872</v>
+        <v>1304.398193272347</v>
       </c>
       <c r="K104" t="n">
-        <v>5060.630087918068</v>
+        <v>1206.488057692482</v>
       </c>
       <c r="L104" t="n">
-        <v>4361.509267460705</v>
+        <v>1125.825358523689</v>
       </c>
       <c r="M104" t="n">
-        <v>3835.599604478092</v>
+        <v>1062.969814372333</v>
       </c>
       <c r="N104" t="n">
-        <v>3412.291578718532</v>
+        <v>1007.869136272664</v>
       </c>
       <c r="O104" t="n">
-        <v>3058.416126517117</v>
+        <v>956.983978242129</v>
       </c>
       <c r="P104" t="n">
-        <v>2768.460457608829</v>
+        <v>913.1890474068318</v>
       </c>
       <c r="Q104" t="n">
-        <v>2534.026384178593</v>
+        <v>877.570168688927</v>
       </c>
       <c r="R104" t="n">
-        <v>2323.82510171472</v>
+        <v>842.325509638462</v>
       </c>
       <c r="S104" t="n">
-        <v>2136.131693050237</v>
+        <v>808.6666691580674</v>
       </c>
       <c r="T104" t="n">
-        <v>1969.028830719439</v>
+        <v>777.2355661468284</v>
       </c>
       <c r="U104" t="n">
-        <v>1818.365437883744</v>
+        <v>747.7947465096255</v>
       </c>
       <c r="V104" t="n">
-        <v>1681.20263644664</v>
+        <v>719.9470703997871</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1625.722294299386</v>
+        <v>2961.787241453912</v>
       </c>
       <c r="F105" t="n">
-        <v>1491.574049258364</v>
+        <v>2670.379144412924</v>
       </c>
       <c r="G105" t="n">
-        <v>1320.176088887577</v>
+        <v>2341.473259377116</v>
       </c>
       <c r="H105" t="n">
-        <v>1170.889073379197</v>
+        <v>2049.825678958443</v>
       </c>
       <c r="I105" t="n">
-        <v>1065.044548367431</v>
+        <v>1834.267417017141</v>
       </c>
       <c r="J105" t="n">
-        <v>996.1071024561794</v>
+        <v>1682.482573218858</v>
       </c>
       <c r="K105" t="n">
-        <v>1023.926951737083</v>
+        <v>1559.804084547822</v>
       </c>
       <c r="L105" t="n">
-        <v>1041.904740480982</v>
+        <v>1458.793049805111</v>
       </c>
       <c r="M105" t="n">
-        <v>1055.543494391792</v>
+        <v>1379.741758004721</v>
       </c>
       <c r="N105" t="n">
-        <v>1060.767542402173</v>
+        <v>1309.745497369128</v>
       </c>
       <c r="O105" t="n">
-        <v>1058.497415423675</v>
+        <v>1244.603797199172</v>
       </c>
       <c r="P105" t="n">
-        <v>1055.202739093754</v>
+        <v>1188.339234277651</v>
       </c>
       <c r="Q105" t="n">
-        <v>1054.251181123842</v>
+        <v>1142.45101742794</v>
       </c>
       <c r="R105" t="n">
-        <v>1047.297914692126</v>
+        <v>1096.821919179154</v>
       </c>
       <c r="S105" t="n">
-        <v>1035.802873467947</v>
+        <v>1053.003952947608</v>
       </c>
       <c r="T105" t="n">
-        <v>1021.310590684863</v>
+        <v>1011.880828959721</v>
       </c>
       <c r="U105" t="n">
-        <v>1004.513672718057</v>
+        <v>973.3302774784466</v>
       </c>
       <c r="V105" t="n">
-        <v>986.6593928222443</v>
+        <v>937.1313204922236</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1905.020239984337</v>
+        <v>3050.43575641097</v>
       </c>
       <c r="F106" t="n">
-        <v>1609.193897518045</v>
+        <v>2747.209303917708</v>
       </c>
       <c r="G106" t="n">
-        <v>1314.458927695274</v>
+        <v>2398.967439553112</v>
       </c>
       <c r="H106" t="n">
-        <v>1093.895432409794</v>
+        <v>2089.93460341948</v>
       </c>
       <c r="I106" t="n">
-        <v>946.700545390093</v>
+        <v>1860.803169589401</v>
       </c>
       <c r="J106" t="n">
-        <v>850.0947832989339</v>
+        <v>1698.014002934731</v>
       </c>
       <c r="K106" t="n">
-        <v>846.3291148855744</v>
+        <v>1566.172812146314</v>
       </c>
       <c r="L106" t="n">
-        <v>841.9243869649833</v>
+        <v>1457.853569277695</v>
       </c>
       <c r="M106" t="n">
-        <v>840.4697976290643</v>
+        <v>1373.11606491534</v>
       </c>
       <c r="N106" t="n">
-        <v>836.7431133370746</v>
+        <v>1298.633067143958</v>
       </c>
       <c r="O106" t="n">
-        <v>829.5225984600814</v>
+        <v>1229.792859190968</v>
       </c>
       <c r="P106" t="n">
-        <v>822.6460538717757</v>
+        <v>1170.1984314858</v>
       </c>
       <c r="Q106" t="n">
-        <v>818.2465334611711</v>
+        <v>1121.139555519715</v>
       </c>
       <c r="R106" t="n">
-        <v>809.7487218652868</v>
+        <v>1072.650313395142</v>
       </c>
       <c r="S106" t="n">
-        <v>798.1608437483752</v>
+        <v>1026.260876769082</v>
       </c>
       <c r="T106" t="n">
-        <v>783.9336728301391</v>
+        <v>982.6727236238089</v>
       </c>
       <c r="U106" t="n">
-        <v>767.725514322689</v>
+        <v>941.7404897803456</v>
       </c>
       <c r="V106" t="n">
-        <v>751.0910528955982</v>
+        <v>903.3101154750686</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>617.603452602735</v>
+        <v>3024.348670729547</v>
       </c>
       <c r="F107" t="n">
-        <v>522.0763233986817</v>
+        <v>2687.00324865597</v>
       </c>
       <c r="G107" t="n">
-        <v>460.2461302067338</v>
+        <v>2330.039536653521</v>
       </c>
       <c r="H107" t="n">
-        <v>411.4869135880344</v>
+        <v>2021.06676038974</v>
       </c>
       <c r="I107" t="n">
-        <v>374.6772896914403</v>
+        <v>1792.812527431944</v>
       </c>
       <c r="J107" t="n">
-        <v>346.5950827442623</v>
+        <v>1629.476333392155</v>
       </c>
       <c r="K107" t="n">
-        <v>350.3170905397644</v>
+        <v>1496.321594693414</v>
       </c>
       <c r="L107" t="n">
-        <v>350.6194588606524</v>
+        <v>1386.057594153008</v>
       </c>
       <c r="M107" t="n">
-        <v>350.9976147925009</v>
+        <v>1298.894134716529</v>
       </c>
       <c r="N107" t="n">
-        <v>350.1964269268959</v>
+        <v>1222.157162658765</v>
       </c>
       <c r="O107" t="n">
-        <v>347.7132242821971</v>
+        <v>1151.402346805693</v>
       </c>
       <c r="P107" t="n">
-        <v>345.105621900709</v>
+        <v>1089.772624038243</v>
       </c>
       <c r="Q107" t="n">
-        <v>343.4332431476156</v>
+        <v>1038.34361304202</v>
       </c>
       <c r="R107" t="n">
-        <v>340.2136208431793</v>
+        <v>987.9012203260678</v>
       </c>
       <c r="S107" t="n">
-        <v>336.3002070509781</v>
+        <v>940.014824283644</v>
       </c>
       <c r="T107" t="n">
-        <v>332.3612934052397</v>
+        <v>895.498964105863</v>
       </c>
       <c r="U107" t="n">
-        <v>328.3087572129518</v>
+        <v>854.067479803035</v>
       </c>
       <c r="V107" t="n">
-        <v>323.9251685084057</v>
+        <v>815.2147458053183</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1318.777341735823</v>
+        <v>3486.114094278604</v>
       </c>
       <c r="F108" t="n">
-        <v>1180.987649937288</v>
+        <v>3120.137347378094</v>
       </c>
       <c r="G108" t="n">
-        <v>1058.849072906836</v>
+        <v>2722.483209888498</v>
       </c>
       <c r="H108" t="n">
-        <v>951.7382551720744</v>
+        <v>2374.323508054176</v>
       </c>
       <c r="I108" t="n">
-        <v>870.7943026332131</v>
+        <v>2116.813049874437</v>
       </c>
       <c r="J108" t="n">
-        <v>810.1973401850676</v>
+        <v>1933.226371431769</v>
       </c>
       <c r="K108" t="n">
-        <v>823.7805016057591</v>
+        <v>1783.516023906744</v>
       </c>
       <c r="L108" t="n">
-        <v>828.4676858297377</v>
+        <v>1659.53993879354</v>
       </c>
       <c r="M108" t="n">
-        <v>831.9796531170127</v>
+        <v>1561.999561005633</v>
       </c>
       <c r="N108" t="n">
-        <v>831.0160219164504</v>
+        <v>1475.971715393558</v>
       </c>
       <c r="O108" t="n">
-        <v>825.0699348038305</v>
+        <v>1396.292967421017</v>
       </c>
       <c r="P108" t="n">
-        <v>817.3222623661795</v>
+        <v>1326.855072989019</v>
       </c>
       <c r="Q108" t="n">
-        <v>810.1813621898926</v>
+        <v>1269.104088140228</v>
       </c>
       <c r="R108" t="n">
-        <v>797.9423376208687</v>
+        <v>1211.879426101133</v>
       </c>
       <c r="S108" t="n">
-        <v>782.967527419952</v>
+        <v>1157.191689354348</v>
       </c>
       <c r="T108" t="n">
-        <v>767.4797353115572</v>
+        <v>1106.228671152887</v>
       </c>
       <c r="U108" t="n">
-        <v>752.3122761850931</v>
+        <v>1058.873987934823</v>
       </c>
       <c r="V108" t="n">
-        <v>736.7172715854414</v>
+        <v>1014.431696737748</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>16547.48478269524</v>
+        <v>3356.895349231764</v>
       </c>
       <c r="F109" t="n">
-        <v>14723.47542553747</v>
+        <v>3047.58735743211</v>
       </c>
       <c r="G109" t="n">
-        <v>12254.40534916717</v>
+        <v>2675.425495968379</v>
       </c>
       <c r="H109" t="n">
-        <v>10003.38451354755</v>
+        <v>2333.989620085172</v>
       </c>
       <c r="I109" t="n">
-        <v>8315.478076046036</v>
+        <v>2075.270285771528</v>
       </c>
       <c r="J109" t="n">
-        <v>7162.48268107599</v>
+        <v>1889.590610832608</v>
       </c>
       <c r="K109" t="n">
-        <v>5898.68096799895</v>
+        <v>1739.148744427516</v>
       </c>
       <c r="L109" t="n">
-        <v>4991.421723287498</v>
+        <v>1615.927456870939</v>
       </c>
       <c r="M109" t="n">
-        <v>4336.830727188461</v>
+        <v>1519.895417119269</v>
       </c>
       <c r="N109" t="n">
-        <v>3825.157229179292</v>
+        <v>1435.953114177196</v>
       </c>
       <c r="O109" t="n">
-        <v>3405.238823770797</v>
+        <v>1358.697201513541</v>
       </c>
       <c r="P109" t="n">
-        <v>3063.608278966998</v>
+        <v>1291.885270938319</v>
       </c>
       <c r="Q109" t="n">
-        <v>2788.111011619203</v>
+        <v>1236.8878776677</v>
       </c>
       <c r="R109" t="n">
-        <v>2544.499775136043</v>
+        <v>1182.786042799136</v>
       </c>
       <c r="S109" t="n">
-        <v>2329.778666514456</v>
+        <v>1131.319864125012</v>
       </c>
       <c r="T109" t="n">
-        <v>2140.303644078267</v>
+        <v>1083.336592469554</v>
       </c>
       <c r="U109" t="n">
-        <v>1971.122946409258</v>
+        <v>1038.511157454225</v>
       </c>
       <c r="V109" t="n">
-        <v>1818.646563606251</v>
+        <v>996.2936553660466</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1498.605106139621</v>
+        <v>4000.521142294769</v>
       </c>
       <c r="F110" t="n">
-        <v>1297.753394115454</v>
+        <v>3576.506859527329</v>
       </c>
       <c r="G110" t="n">
-        <v>1101.264489435974</v>
+        <v>3112.428450152789</v>
       </c>
       <c r="H110" t="n">
-        <v>949.251771119276</v>
+        <v>2706.487884707351</v>
       </c>
       <c r="I110" t="n">
-        <v>847.9588303995342</v>
+        <v>2406.884479872083</v>
       </c>
       <c r="J110" t="n">
-        <v>782.6436635106454</v>
+        <v>2194.138448353887</v>
       </c>
       <c r="K110" t="n">
-        <v>798.2152553325765</v>
+        <v>2021.948862085556</v>
       </c>
       <c r="L110" t="n">
-        <v>809.7712666678618</v>
+        <v>1880.244059463696</v>
       </c>
       <c r="M110" t="n">
-        <v>820.5089423006514</v>
+        <v>1768.950137511275</v>
       </c>
       <c r="N110" t="n">
-        <v>824.7864061435762</v>
+        <v>1670.641643085743</v>
       </c>
       <c r="O110" t="n">
-        <v>821.8914821635735</v>
+        <v>1579.372702472875</v>
       </c>
       <c r="P110" t="n">
-        <v>817.0518654485367</v>
+        <v>1499.872832466377</v>
       </c>
       <c r="Q110" t="n">
-        <v>813.8698145642152</v>
+        <v>1433.968372927572</v>
       </c>
       <c r="R110" t="n">
-        <v>806.5259863877334</v>
+        <v>1369.02485785043</v>
       </c>
       <c r="S110" t="n">
-        <v>796.2372586886055</v>
+        <v>1307.077078986937</v>
       </c>
       <c r="T110" t="n">
-        <v>784.1162583199871</v>
+        <v>1249.19547919302</v>
       </c>
       <c r="U110" t="n">
-        <v>770.8047983572362</v>
+        <v>1195.154756560631</v>
       </c>
       <c r="V110" t="n">
-        <v>756.5113224267709</v>
+        <v>1144.371674056784</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>11710.93267332648</v>
+        <v>2607.638532863194</v>
       </c>
       <c r="F111" t="n">
-        <v>10249.27010986072</v>
+        <v>2359.343409459746</v>
       </c>
       <c r="G111" t="n">
-        <v>8820.868227372977</v>
+        <v>2072.424429243398</v>
       </c>
       <c r="H111" t="n">
-        <v>7651.476790618127</v>
+        <v>1815.812684990635</v>
       </c>
       <c r="I111" t="n">
-        <v>6803.004461638282</v>
+        <v>1624.803672115796</v>
       </c>
       <c r="J111" t="n">
-        <v>6206.621434242395</v>
+        <v>1489.047123215875</v>
       </c>
       <c r="K111" t="n">
-        <v>5342.927725042579</v>
+        <v>1378.654537258109</v>
       </c>
       <c r="L111" t="n">
-        <v>4666.314468799646</v>
+        <v>1287.603531065672</v>
       </c>
       <c r="M111" t="n">
-        <v>4136.843474658042</v>
+        <v>1216.196563324959</v>
       </c>
       <c r="N111" t="n">
-        <v>3694.620121745164</v>
+        <v>1153.052443464698</v>
       </c>
       <c r="O111" t="n">
-        <v>3318.516948895217</v>
+        <v>1094.507817180858</v>
       </c>
       <c r="P111" t="n">
-        <v>3011.66716326759</v>
+        <v>1044.214807633765</v>
       </c>
       <c r="Q111" t="n">
-        <v>2766.679225500707</v>
+        <v>1003.517491924879</v>
       </c>
       <c r="R111" t="n">
-        <v>2548.259081577876</v>
+        <v>963.4447283688173</v>
       </c>
       <c r="S111" t="n">
-        <v>2352.947490336159</v>
+        <v>925.2727750801922</v>
       </c>
       <c r="T111" t="n">
-        <v>2175.282037207183</v>
+        <v>889.4132460513516</v>
       </c>
       <c r="U111" t="n">
-        <v>2011.797405259587</v>
+        <v>855.5906213564724</v>
       </c>
       <c r="V111" t="n">
-        <v>1864.021034898624</v>
+        <v>823.7611129824222</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1585.437611962088</v>
+        <v>2531.392411082509</v>
       </c>
       <c r="F112" t="n">
-        <v>1378.82765527771</v>
+        <v>2283.065098258056</v>
       </c>
       <c r="G112" t="n">
-        <v>1165.394583529218</v>
+        <v>1998.665726121727</v>
       </c>
       <c r="H112" t="n">
-        <v>992.9830834772554</v>
+        <v>1745.29120838008</v>
       </c>
       <c r="I112" t="n">
-        <v>871.2058117617906</v>
+        <v>1556.879939005963</v>
       </c>
       <c r="J112" t="n">
-        <v>787.8602207199974</v>
+        <v>1422.818845310309</v>
       </c>
       <c r="K112" t="n">
-        <v>787.0677846230918</v>
+        <v>1314.016728397793</v>
       </c>
       <c r="L112" t="n">
-        <v>783.5446303042052</v>
+        <v>1224.436988323941</v>
       </c>
       <c r="M112" t="n">
-        <v>781.748804218543</v>
+        <v>1154.339101728349</v>
       </c>
       <c r="N112" t="n">
-        <v>776.4493460413481</v>
+        <v>1092.477468061867</v>
       </c>
       <c r="O112" t="n">
-        <v>766.4615946274853</v>
+        <v>1034.961920818944</v>
       </c>
       <c r="P112" t="n">
-        <v>755.3042884484577</v>
+        <v>984.833105329579</v>
       </c>
       <c r="Q112" t="n">
-        <v>745.5218191967763</v>
+        <v>943.2883477852141</v>
       </c>
       <c r="R112" t="n">
-        <v>731.8757163127767</v>
+        <v>902.079841241012</v>
       </c>
       <c r="S112" t="n">
-        <v>716.2697467734918</v>
+        <v>862.6827798409103</v>
       </c>
       <c r="T112" t="n">
-        <v>700.346240952479</v>
+        <v>825.9514136065461</v>
       </c>
       <c r="U112" t="n">
-        <v>684.4842325122104</v>
+        <v>791.7610319785545</v>
       </c>
       <c r="V112" t="n">
-        <v>668.5315176957653</v>
+        <v>759.6888859824508</v>
       </c>
     </row>
     <row r="113">
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>33871.36554102324</v>
+        <v>7011.896821488919</v>
       </c>
       <c r="F116" t="n">
-        <v>29469.69777277949</v>
+        <v>6571.259188902894</v>
       </c>
       <c r="G116" t="n">
-        <v>26302.05056977795</v>
+        <v>6119.789421133853</v>
       </c>
       <c r="H116" t="n">
-        <v>23970.30424169494</v>
+        <v>5684.270270574327</v>
       </c>
       <c r="I116" t="n">
-        <v>22416.11197653863</v>
+        <v>5319.976822475656</v>
       </c>
       <c r="J116" t="n">
-        <v>20612.71864794144</v>
+        <v>4844.506181410633</v>
       </c>
       <c r="K116" t="n">
-        <v>19594.93610823965</v>
+        <v>4536.930889184328</v>
       </c>
       <c r="L116" t="n">
-        <v>18692.15645316728</v>
+        <v>4261.927656985494</v>
       </c>
       <c r="M116" t="n">
-        <v>17942.88727780435</v>
+        <v>4038.039765925748</v>
       </c>
       <c r="N116" t="n">
-        <v>17073.20439455689</v>
+        <v>3757.854125507223</v>
       </c>
       <c r="O116" t="n">
-        <v>16068.88086768938</v>
+        <v>3447.629809231468</v>
       </c>
       <c r="P116" t="n">
-        <v>15124.51934187692</v>
+        <v>3172.828167408202</v>
       </c>
       <c r="Q116" t="n">
-        <v>14332.0828245396</v>
+        <v>2955.943681283753</v>
       </c>
       <c r="R116" t="n">
-        <v>13561.16781044982</v>
+        <v>2759.301654133846</v>
       </c>
       <c r="S116" t="n">
-        <v>12831.18459950143</v>
+        <v>2581.68929624893</v>
       </c>
       <c r="T116" t="n">
-        <v>12143.14517569012</v>
+        <v>2422.188837383897</v>
       </c>
       <c r="U116" t="n">
-        <v>11486.12364355951</v>
+        <v>2277.667194264739</v>
       </c>
       <c r="V116" t="n">
-        <v>10873.04855203637</v>
+        <v>2149.898629607369</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>19318.92935211125</v>
+        <v>3999.317333545318</v>
       </c>
       <c r="F117" t="n">
-        <v>16753.25127364915</v>
+        <v>3735.700217376787</v>
       </c>
       <c r="G117" t="n">
-        <v>14908.97419914583</v>
+        <v>3468.92278765897</v>
       </c>
       <c r="H117" t="n">
-        <v>13553.23993742815</v>
+        <v>3213.98836117325</v>
       </c>
       <c r="I117" t="n">
-        <v>12647.39802136254</v>
+        <v>3001.584949643152</v>
       </c>
       <c r="J117" t="n">
-        <v>11608.26447031619</v>
+        <v>2728.233472862766</v>
       </c>
       <c r="K117" t="n">
-        <v>11017.11771385706</v>
+        <v>2550.85810894594</v>
       </c>
       <c r="L117" t="n">
-        <v>10494.01311595819</v>
+        <v>2392.700106244492</v>
       </c>
       <c r="M117" t="n">
-        <v>10060.61258353321</v>
+        <v>2264.136928063546</v>
       </c>
       <c r="N117" t="n">
-        <v>9568.802969196975</v>
+        <v>2106.116982086287</v>
       </c>
       <c r="O117" t="n">
-        <v>9006.320969962226</v>
+        <v>1932.334983571774</v>
       </c>
       <c r="P117" t="n">
-        <v>8477.785924620861</v>
+        <v>1778.473574657896</v>
       </c>
       <c r="Q117" t="n">
-        <v>8032.919438752694</v>
+        <v>1656.762506037231</v>
       </c>
       <c r="R117" t="n">
-        <v>7599.542602209672</v>
+        <v>1546.285007761924</v>
       </c>
       <c r="S117" t="n">
-        <v>7189.155277957459</v>
+        <v>1446.488832438611</v>
       </c>
       <c r="T117" t="n">
-        <v>6802.133823084097</v>
+        <v>1356.819207734312</v>
       </c>
       <c r="U117" t="n">
-        <v>6432.101218983538</v>
+        <v>1275.468242494032</v>
       </c>
       <c r="V117" t="n">
-        <v>6085.880775835368</v>
+        <v>1203.344828021075</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>19305.63167667729</v>
+        <v>3996.564508954095</v>
       </c>
       <c r="F118" t="n">
-        <v>16740.85610214223</v>
+        <v>3732.936297454011</v>
       </c>
       <c r="G118" t="n">
-        <v>14904.49147543253</v>
+        <v>3467.879776775113</v>
       </c>
       <c r="H118" t="n">
-        <v>13556.03095764863</v>
+        <v>3214.65021815064</v>
       </c>
       <c r="I118" t="n">
-        <v>12655.44734827333</v>
+        <v>3003.49528238217</v>
       </c>
       <c r="J118" t="n">
-        <v>11619.98949975409</v>
+        <v>2730.989149034731</v>
       </c>
       <c r="K118" t="n">
-        <v>11032.09973622721</v>
+        <v>2554.32698476272</v>
       </c>
       <c r="L118" t="n">
-        <v>10512.19290290772</v>
+        <v>2396.845210474914</v>
       </c>
       <c r="M118" t="n">
-        <v>10081.33755765996</v>
+        <v>2268.801075389369</v>
       </c>
       <c r="N118" t="n">
-        <v>9590.936618247923</v>
+        <v>2110.988652482371</v>
       </c>
       <c r="O118" t="n">
-        <v>9028.713002604918</v>
+        <v>1937.139265825395</v>
       </c>
       <c r="P118" t="n">
-        <v>8500.04617420399</v>
+        <v>1783.143339381078</v>
       </c>
       <c r="Q118" t="n">
-        <v>8055.088117732751</v>
+        <v>1661.334721216364</v>
       </c>
       <c r="R118" t="n">
-        <v>7621.515388928753</v>
+        <v>1550.755828232915</v>
       </c>
       <c r="S118" t="n">
-        <v>7210.814574693974</v>
+        <v>1450.846775705391</v>
       </c>
       <c r="T118" t="n">
-        <v>6823.222640555556</v>
+        <v>1361.025786632382</v>
       </c>
       <c r="U118" t="n">
-        <v>6452.437159283482</v>
+        <v>1279.500804347838</v>
       </c>
       <c r="V118" t="n">
-        <v>6105.67476762254</v>
+        <v>1207.258640748655</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>20450.43066378998</v>
+        <v>4233.555614865238</v>
       </c>
       <c r="F119" t="n">
-        <v>17745.06620288095</v>
+        <v>3956.858677079674</v>
       </c>
       <c r="G119" t="n">
-        <v>15789.01992447713</v>
+        <v>3673.686081906495</v>
       </c>
       <c r="H119" t="n">
-        <v>14346.36750026474</v>
+        <v>3402.069053874239</v>
       </c>
       <c r="I119" t="n">
-        <v>13380.62708125591</v>
+        <v>3175.600925657309</v>
       </c>
       <c r="J119" t="n">
-        <v>12276.02797077562</v>
+        <v>2885.174653742762</v>
       </c>
       <c r="K119" t="n">
-        <v>11647.51006666524</v>
+        <v>2696.816560752253</v>
       </c>
       <c r="L119" t="n">
-        <v>11092.47663101557</v>
+        <v>2529.153501178699</v>
       </c>
       <c r="M119" t="n">
-        <v>10632.71466352124</v>
+        <v>2392.888277464222</v>
       </c>
       <c r="N119" t="n">
-        <v>10110.94818184132</v>
+        <v>2225.444471931751</v>
       </c>
       <c r="O119" t="n">
-        <v>9513.938506992035</v>
+        <v>2041.245950478409</v>
       </c>
       <c r="P119" t="n">
-        <v>8952.962579822468</v>
+        <v>1878.156337591563</v>
       </c>
       <c r="Q119" t="n">
-        <v>8480.888449212094</v>
+        <v>1749.154601596107</v>
       </c>
       <c r="R119" t="n">
-        <v>8021.377207315372</v>
+        <v>1632.116032036019</v>
       </c>
       <c r="S119" t="n">
-        <v>7586.378732228046</v>
+        <v>1526.411892713718</v>
       </c>
       <c r="T119" t="n">
-        <v>7176.067963381088</v>
+        <v>1431.407717336379</v>
       </c>
       <c r="U119" t="n">
-        <v>6783.801489624657</v>
+        <v>1345.209453149576</v>
       </c>
       <c r="V119" t="n">
-        <v>6417.068847420564</v>
+        <v>1268.829754155403</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>20846.53013526883</v>
+        <v>4315.554335089241</v>
       </c>
       <c r="F120" t="n">
-        <v>18100.20057854067</v>
+        <v>4036.047817282197</v>
       </c>
       <c r="G120" t="n">
-        <v>16126.82932097387</v>
+        <v>3752.285367011636</v>
       </c>
       <c r="H120" t="n">
-        <v>14674.47472047718</v>
+        <v>3479.875747514465</v>
       </c>
       <c r="I120" t="n">
-        <v>13703.44485512782</v>
+        <v>3252.214705791875</v>
       </c>
       <c r="J120" t="n">
-        <v>12584.05549293756</v>
+        <v>2957.568851749406</v>
       </c>
       <c r="K120" t="n">
-        <v>11947.49063952898</v>
+        <v>2766.272828451923</v>
       </c>
       <c r="L120" t="n">
-        <v>11383.11992277571</v>
+        <v>2595.42197514049</v>
       </c>
       <c r="M120" t="n">
-        <v>10914.07256230522</v>
+        <v>2456.207762594473</v>
       </c>
       <c r="N120" t="n">
-        <v>10375.16003952041</v>
+        <v>2283.598149237524</v>
       </c>
       <c r="O120" t="n">
-        <v>9756.891601779844</v>
+        <v>2093.372314391914</v>
       </c>
       <c r="P120" t="n">
-        <v>9176.281527134513</v>
+        <v>1925.004282322681</v>
       </c>
       <c r="Q120" t="n">
-        <v>8688.392237808215</v>
+        <v>1791.951557227421</v>
       </c>
       <c r="R120" t="n">
-        <v>8214.133204005408</v>
+        <v>1671.336248761409</v>
       </c>
       <c r="S120" t="n">
-        <v>7765.265453529726</v>
+        <v>1562.404667189206</v>
       </c>
       <c r="T120" t="n">
-        <v>7342.211904640077</v>
+        <v>1464.548390047551</v>
       </c>
       <c r="U120" t="n">
-        <v>6938.279991250116</v>
+        <v>1375.842121431612</v>
       </c>
       <c r="V120" t="n">
-        <v>6561.19873963596</v>
+        <v>1297.328169876824</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>17617.87864043782</v>
+        <v>3647.173512714404</v>
       </c>
       <c r="F121" t="n">
-        <v>15291.6389346191</v>
+        <v>3409.784641736404</v>
       </c>
       <c r="G121" t="n">
-        <v>13608.86723576499</v>
+        <v>3166.422386804239</v>
       </c>
       <c r="H121" t="n">
-        <v>12370.06615340742</v>
+        <v>2933.412883375712</v>
       </c>
       <c r="I121" t="n">
-        <v>11543.84559356506</v>
+        <v>2739.680773559416</v>
       </c>
       <c r="J121" t="n">
-        <v>10598.26771559626</v>
+        <v>2490.858888511676</v>
       </c>
       <c r="K121" t="n">
-        <v>10063.4790316136</v>
+        <v>2330.056531908479</v>
       </c>
       <c r="L121" t="n">
-        <v>9591.95449707537</v>
+        <v>2187.025143828421</v>
       </c>
       <c r="M121" t="n">
-        <v>9201.686651768907</v>
+        <v>2070.835982977848</v>
       </c>
       <c r="N121" t="n">
-        <v>8756.610016531135</v>
+        <v>1927.351322906683</v>
       </c>
       <c r="O121" t="n">
-        <v>8245.270975456571</v>
+        <v>1769.049271954722</v>
       </c>
       <c r="P121" t="n">
-        <v>7764.246116825807</v>
+        <v>1628.786887127531</v>
       </c>
       <c r="Q121" t="n">
-        <v>7359.563214766169</v>
+        <v>1517.885058852322</v>
       </c>
       <c r="R121" t="n">
-        <v>6965.192961843137</v>
+        <v>1417.213379383478</v>
       </c>
       <c r="S121" t="n">
-        <v>6591.52787251191</v>
+        <v>1326.243638876697</v>
       </c>
       <c r="T121" t="n">
-        <v>6238.776064314787</v>
+        <v>1244.446436511801</v>
       </c>
       <c r="U121" t="n">
-        <v>5901.201672712774</v>
+        <v>1170.192301057662</v>
       </c>
       <c r="V121" t="n">
-        <v>5585.470905149525</v>
+        <v>1104.40013094929</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>187.6211551737626</v>
+        <v>4973.370000168219</v>
       </c>
       <c r="F122" t="n">
-        <v>302.8099805534155</v>
+        <v>4649.142562740002</v>
       </c>
       <c r="G122" t="n">
-        <v>376.9683013341145</v>
+        <v>4321.111143293328</v>
       </c>
       <c r="H122" t="n">
-        <v>430.3871092095076</v>
+        <v>4006.411545501554</v>
       </c>
       <c r="I122" t="n">
-        <v>475.8856598983718</v>
+        <v>3743.146514762943</v>
       </c>
       <c r="J122" t="n">
-        <v>499.5411009721603</v>
+        <v>3402.721507939998</v>
       </c>
       <c r="K122" t="n">
-        <v>529.1570853964108</v>
+        <v>3181.22728675021</v>
       </c>
       <c r="L122" t="n">
-        <v>553.658383141975</v>
+        <v>2983.327390150354</v>
       </c>
       <c r="M122" t="n">
-        <v>575.8033251512102</v>
+        <v>2821.9383759093</v>
       </c>
       <c r="N122" t="n">
-        <v>580.2811593233715</v>
+        <v>2622.217112694326</v>
       </c>
       <c r="O122" t="n">
-        <v>571.1623472425089</v>
+        <v>2402.510827124655</v>
       </c>
       <c r="P122" t="n">
-        <v>560.4412292407391</v>
+        <v>2208.185330523243</v>
       </c>
       <c r="Q122" t="n">
-        <v>554.2739576644785</v>
+        <v>2054.60815129988</v>
       </c>
       <c r="R122" t="n">
-        <v>547.3470842260524</v>
+        <v>1915.451431530527</v>
       </c>
       <c r="S122" t="n">
-        <v>540.2378865347071</v>
+        <v>1789.80567233391</v>
       </c>
       <c r="T122" t="n">
-        <v>533.6671998497586</v>
+        <v>1676.948970841518</v>
       </c>
       <c r="U122" t="n">
-        <v>527.4501586084822</v>
+        <v>1574.658980977789</v>
       </c>
       <c r="V122" t="n">
-        <v>522.4404089156433</v>
+        <v>1484.10970747349</v>
       </c>
     </row>
     <row r="123">
@@ -9722,58 +9722,58 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5709.903867467754</v>
+        <v>10875.33506461774</v>
       </c>
       <c r="F123" t="n">
-        <v>5177.558977962617</v>
+        <v>9696.259046672085</v>
       </c>
       <c r="G123" t="n">
-        <v>4623.250645596134</v>
+        <v>8769.135668911929</v>
       </c>
       <c r="H123" t="n">
-        <v>4117.474650076048</v>
+        <v>7872.425645719634</v>
       </c>
       <c r="I123" t="n">
-        <v>3697.488666271875</v>
+        <v>7117.98105754417</v>
       </c>
       <c r="J123" t="n">
-        <v>3383.808828569386</v>
+        <v>6538.770523181491</v>
       </c>
       <c r="K123" t="n">
-        <v>3132.91801231317</v>
+        <v>6065.487822394637</v>
       </c>
       <c r="L123" t="n">
-        <v>2910.676207221707</v>
+        <v>5642.990870629659</v>
       </c>
       <c r="M123" t="n">
-        <v>2720.928259498032</v>
+        <v>5288.009762809342</v>
       </c>
       <c r="N123" t="n">
-        <v>2545.336501998417</v>
+        <v>4964.285145571706</v>
       </c>
       <c r="O123" t="n">
-        <v>2372.609581609777</v>
+        <v>4643.545930918866</v>
       </c>
       <c r="P123" t="n">
-        <v>2217.454044196711</v>
+        <v>4349.007930271068</v>
       </c>
       <c r="Q123" t="n">
-        <v>2084.257792904539</v>
+        <v>4087.752100624328</v>
       </c>
       <c r="R123" t="n">
-        <v>1962.362284340571</v>
+        <v>3840.747387455299</v>
       </c>
       <c r="S123" t="n">
-        <v>1851.071676975359</v>
+        <v>3609.434164830002</v>
       </c>
       <c r="T123" t="n">
-        <v>1749.817570775959</v>
+        <v>3393.127182892223</v>
       </c>
       <c r="U123" t="n">
-        <v>1655.984655304289</v>
+        <v>3190.289245400386</v>
       </c>
       <c r="V123" t="n">
-        <v>1571.581118365872</v>
+        <v>3003.138171486262</v>
       </c>
     </row>
     <row r="124">
@@ -9798,58 +9798,58 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2972.252748187202</v>
+        <v>3824.431817506784</v>
       </c>
       <c r="F124" t="n">
-        <v>2652.072577926007</v>
+        <v>3452.143810971967</v>
       </c>
       <c r="G124" t="n">
-        <v>2391.812949249376</v>
+        <v>3154.998554327697</v>
       </c>
       <c r="H124" t="n">
-        <v>2157.358588735683</v>
+        <v>2859.586839686397</v>
       </c>
       <c r="I124" t="n">
-        <v>1974.637454839017</v>
+        <v>2610.144612917611</v>
       </c>
       <c r="J124" t="n">
-        <v>1846.430776376164</v>
+        <v>2420.886907051466</v>
       </c>
       <c r="K124" t="n">
-        <v>1749.031497638256</v>
+        <v>2267.853109071492</v>
       </c>
       <c r="L124" t="n">
-        <v>1664.34441443493</v>
+        <v>2131.421152839974</v>
       </c>
       <c r="M124" t="n">
-        <v>1596.15319802048</v>
+        <v>2018.388710775284</v>
       </c>
       <c r="N124" t="n">
-        <v>1532.892170546018</v>
+        <v>1915.099029562246</v>
       </c>
       <c r="O124" t="n">
-        <v>1465.067201967654</v>
+        <v>1810.273285314238</v>
       </c>
       <c r="P124" t="n">
-        <v>1400.128073784743</v>
+        <v>1713.03089496541</v>
       </c>
       <c r="Q124" t="n">
-        <v>1341.613970105616</v>
+        <v>1626.653941330145</v>
       </c>
       <c r="R124" t="n">
-        <v>1284.33186158694</v>
+        <v>1543.987117805435</v>
       </c>
       <c r="S124" t="n">
-        <v>1229.101709811044</v>
+        <v>1465.794610378106</v>
       </c>
       <c r="T124" t="n">
-        <v>1176.582170448723</v>
+        <v>1392.058919136699</v>
       </c>
       <c r="U124" t="n">
-        <v>1126.197620699584</v>
+        <v>1322.363546425393</v>
       </c>
       <c r="V124" t="n">
-        <v>1078.26781835576</v>
+        <v>1257.517950212854</v>
       </c>
     </row>
     <row r="125">
@@ -9874,58 +9874,58 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3860.3545529002</v>
+        <v>2928.022777551922</v>
       </c>
       <c r="F125" t="n">
-        <v>3631.696496665644</v>
+        <v>2700.746429457712</v>
       </c>
       <c r="G125" t="n">
-        <v>3491.030054580316</v>
+        <v>2525.603234162638</v>
       </c>
       <c r="H125" t="n">
-        <v>3288.507444205978</v>
+        <v>2338.853018834453</v>
       </c>
       <c r="I125" t="n">
-        <v>3079.440999217901</v>
+        <v>2175.082698600804</v>
       </c>
       <c r="J125" t="n">
-        <v>2898.018803524174</v>
+        <v>2048.839649583715</v>
       </c>
       <c r="K125" t="n">
-        <v>2734.889611937797</v>
+        <v>1944.001943572826</v>
       </c>
       <c r="L125" t="n">
-        <v>2579.248079166966</v>
+        <v>1847.009501058558</v>
       </c>
       <c r="M125" t="n">
-        <v>2447.218257105102</v>
+        <v>1765.90570986938</v>
       </c>
       <c r="N125" t="n">
-        <v>2326.144003547126</v>
+        <v>1690.281056345973</v>
       </c>
       <c r="O125" t="n">
-        <v>2203.665278146187</v>
+        <v>1610.894781148234</v>
       </c>
       <c r="P125" t="n">
-        <v>2090.964893733417</v>
+        <v>1536.570477258568</v>
       </c>
       <c r="Q125" t="n">
-        <v>1990.804384245885</v>
+        <v>1470.447772775314</v>
       </c>
       <c r="R125" t="n">
-        <v>1893.342609084061</v>
+        <v>1405.981686446941</v>
       </c>
       <c r="S125" t="n">
-        <v>1799.947732069178</v>
+        <v>1344.087382509074</v>
       </c>
       <c r="T125" t="n">
-        <v>1710.411003645314</v>
+        <v>1284.658191201462</v>
       </c>
       <c r="U125" t="n">
-        <v>1625.570500132103</v>
+        <v>1227.936768810697</v>
       </c>
       <c r="V125" t="n">
-        <v>1547.140701590457</v>
+        <v>1175.199376201015</v>
       </c>
     </row>
     <row r="126">
